--- a/public/templates/template-cepat.xlsx
+++ b/public/templates/template-cepat.xlsx
@@ -5,15 +5,16 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0e904f0303665277/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\pas\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3D7CFAE2-0EF9-43AD-989C-B181B23CCC8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32C953AF-DC2C-436C-A903-64ADD695873B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9C6CEF0E-7DB1-444C-9B62-1D49F30FDF33}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Daftar nama dosen" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -71,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="35">
   <si>
     <t>nama</t>
   </si>
@@ -109,16 +110,73 @@
     <t xml:space="preserve"> = Gizi</t>
   </si>
   <si>
-    <t>pagi</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> = Reguler A</t>
-  </si>
-  <si>
     <t>karyawan</t>
   </si>
   <si>
     <t xml:space="preserve"> = Reguler B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	ICTs</t>
+  </si>
+  <si>
+    <t>Nama</t>
+  </si>
+  <si>
+    <t>Prodi</t>
+  </si>
+  <si>
+    <t>Mukhlisiana Ahmad, Sst., M.kes</t>
+  </si>
+  <si>
+    <t>Kebidanan</t>
+  </si>
+  <si>
+    <t>Bdn.Lia Indria Sari, SST., M.Kes</t>
+  </si>
+  <si>
+    <t>Devi Kurniati, M.Keb</t>
+  </si>
+  <si>
+    <t>Ilham Maulana, M.Farm</t>
+  </si>
+  <si>
+    <t>apt. Rahmadhani Tyas A., M.Farm</t>
+  </si>
+  <si>
+    <t>Nabiila Rahmani, M.Si</t>
+  </si>
+  <si>
+    <t>Triswanti, S.SiT., M.Kes</t>
+  </si>
+  <si>
+    <t>Asri Ismiyani Nurlita, M.Gz</t>
+  </si>
+  <si>
+    <t>Widi Siti Rodhiah, M.gizi.</t>
+  </si>
+  <si>
+    <t>Deannisa Fajriaty, S.Si., M.Gz</t>
+  </si>
+  <si>
+    <t>Farmasi</t>
+  </si>
+  <si>
+    <t>Gizi</t>
+  </si>
+  <si>
+    <t>test1</t>
+  </si>
+  <si>
+    <t>test2</t>
+  </si>
+  <si>
+    <t>Bolehkoson1g@sbh.ac.id</t>
+  </si>
+  <si>
+    <t>Bolehkosong2@sbh.ac.id</t>
+  </si>
+  <si>
+    <t>Tahun Masuk</t>
   </si>
 </sst>
 </file>
@@ -512,15 +570,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F18CB60C-B62A-4FA5-B01F-6A78B1372127}">
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="20.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.77734375" customWidth="1"/>
+    <col min="6" max="6" width="19.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -539,8 +598,11 @@
       <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -553,13 +615,59 @@
       <c r="D2">
         <v>15401</v>
       </c>
-    </row>
-    <row r="12" spans="1:6">
+      <c r="F2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3">
+        <v>1234566790</v>
+      </c>
+      <c r="D3">
+        <v>48201</v>
+      </c>
+      <c r="F3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4">
+        <v>1234527890</v>
+      </c>
+      <c r="D4">
+        <v>13211</v>
+      </c>
+      <c r="F4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:7">
       <c r="A13">
         <v>15401</v>
       </c>
@@ -567,7 +675,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:7">
       <c r="A14">
         <v>48201</v>
       </c>
@@ -575,7 +683,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:7">
       <c r="A15">
         <v>13211</v>
       </c>
@@ -583,28 +691,127 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
-      <c r="A16" t="s">
-        <v>12</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>13</v>
-      </c>
+    <row r="16" spans="1:7">
+      <c r="B16" s="4"/>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B17" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1" xr:uid="{60465358-2080-421A-B4AA-4EED12ACEBEC}"/>
+    <hyperlink ref="B3" r:id="rId2" xr:uid="{4FCF878C-1C19-429E-BABF-71C90A8207AC}"/>
+    <hyperlink ref="B4" r:id="rId3" xr:uid="{306C3E86-CDA8-4EAE-BCFD-FB2287D93A40}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
+  <pageSetup orientation="portrait" r:id="rId4"/>
+  <legacyDrawing r:id="rId5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A24EE624-9407-464E-BE88-4F8C93C6EE50}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="26.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" t="s">
+        <v>29</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>